--- a/artfynd/A 49359-2023 artfynd.xlsx
+++ b/artfynd/A 49359-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574093</v>
       </c>
       <c r="B2" t="n">
-        <v>56923</v>
+        <v>56928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49359-2023 artfynd.xlsx
+++ b/artfynd/A 49359-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574093</v>
       </c>
       <c r="B2" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49359-2023 artfynd.xlsx
+++ b/artfynd/A 49359-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574093</v>
       </c>
       <c r="B2" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49359-2023 artfynd.xlsx
+++ b/artfynd/A 49359-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574093</v>
       </c>
       <c r="B2" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
